--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
   <si>
     <t>费用报销单</t>
   </si>
@@ -77,7 +77,7 @@
     </r>
   </si>
   <si>
-    <t>{year}年{month}月{day}日</t>
+    <t>{yearMonthDay}</t>
   </si>
   <si>
     <t>财务收单编码：</t>
@@ -119,7 +119,7 @@
     <t>总计金额（小写）</t>
   </si>
   <si>
-    <t>{lowFeeTotal}</t>
+    <t>￥{lowFeeTotalQian}</t>
   </si>
   <si>
     <t>是否冲借支</t>
@@ -182,9 +182,6 @@
     <t>成本一览表</t>
   </si>
   <si>
-    <t>{sn}</t>
-  </si>
-  <si>
     <t>项目/合同名称</t>
   </si>
   <si>
@@ -218,10 +215,10 @@
     <t>总计进项税额</t>
   </si>
   <si>
-    <t>{taxCostTotal}</t>
-  </si>
-  <si>
-    <t>{lowCostTotal}</t>
+    <t>￥{taxCostTotalQian}</t>
+  </si>
+  <si>
+    <t>￥{lowCostTotalQian}</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1134,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1793,7 +1790,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="36"/>
@@ -1807,7 +1804,7 @@
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:16">
       <c r="A12" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>6</v>
@@ -1816,10 +1813,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>41</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>9</v>
@@ -1836,22 +1833,22 @@
     </row>
     <row r="13" ht="35.1" customHeight="1" spans="1:16">
       <c r="A13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="C13" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="D13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="F13" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>47</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="36"/>
@@ -1868,19 +1865,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="D14" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="E14" s="34" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" ht="35.1" customHeight="1" spans="1:6">

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -1013,7 +1013,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1030,12 +1030,12 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1074,11 +1074,11 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1127,6 +1127,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1521,7 +1525,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.75" style="1" customWidth="1"/>
@@ -1558,15 +1562,15 @@
         <v>5</v>
       </c>
       <c r="H2" s="10"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
     </row>
     <row r="3" ht="35.1" customHeight="1" spans="1:17">
       <c r="A3" s="11" t="s">
@@ -1584,15 +1588,15 @@
         <v>9</v>
       </c>
       <c r="H3" s="10"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:17">
       <c r="A4" s="15" t="s">
@@ -1610,15 +1614,15 @@
         <v>13</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:17">
       <c r="A5" s="18" t="s">
@@ -1636,15 +1640,15 @@
       </c>
       <c r="F5" s="23"/>
       <c r="H5" s="10"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:17">
       <c r="A6" s="24" t="s">
@@ -1666,15 +1670,15 @@
         <v>23</v>
       </c>
       <c r="H6" s="10"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:17">
       <c r="A7" s="24" t="s">
@@ -1692,19 +1696,19 @@
       <c r="E7" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="15" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="10"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:17">
       <c r="A8" s="28" t="s">
@@ -1722,39 +1726,39 @@
       <c r="E8" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="10"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:17">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
       <c r="H9" s="10"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:16">
       <c r="A10" s="4" t="s">
@@ -1766,14 +1770,14 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
     </row>
     <row r="11" ht="35.1" customHeight="1" spans="1:16">
       <c r="A11" s="5" t="s">
@@ -1793,14 +1797,14 @@
         <v>5</v>
       </c>
       <c r="H11" s="10"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:16">
       <c r="A12" s="24" t="s">
@@ -1822,14 +1826,14 @@
         <v>9</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
     </row>
     <row r="13" ht="35.1" customHeight="1" spans="1:16">
       <c r="A13" s="15" t="s">
@@ -1838,7 +1842,7 @@
       <c r="B13" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="32" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="15" t="s">
@@ -1851,32 +1855,32 @@
         <v>46</v>
       </c>
       <c r="H13" s="10"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
     </row>
     <row r="14" ht="35.1" customHeight="1" spans="1:6">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="33" t="s">
         <v>48</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="36" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1896,142 +1900,142 @@
       <c r="E15" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="30" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" ht="50.1" customHeight="1"/>
     <row r="17" ht="54.95" customHeight="1" spans="8:17">
       <c r="H17" s="10"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
     </row>
     <row r="18" ht="39" customHeight="1" spans="8:17">
       <c r="H18" s="10"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
     </row>
     <row r="19" ht="35.1" customHeight="1" spans="8:17">
       <c r="H19" s="10"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
     </row>
     <row r="20" ht="45" customHeight="1" spans="8:17">
       <c r="H20" s="10"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
     </row>
     <row r="21" ht="45" customHeight="1" spans="8:17">
       <c r="H21" s="10"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
     </row>
     <row r="22" ht="45" customHeight="1" spans="8:17">
       <c r="H22" s="10"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="8:17">
       <c r="H23" s="10"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
     </row>
     <row r="24" ht="45" hidden="1" customHeight="1" spans="8:17">
       <c r="H24" s="10"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="37"/>
-      <c r="Q24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
     </row>
     <row r="25" ht="45" hidden="1" customHeight="1" spans="8:17">
       <c r="H25" s="10"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="8:17">
       <c r="H26" s="10"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="37"/>
-      <c r="Q26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="8:17">
       <c r="H27" s="10"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
     </row>
     <row r="28" ht="45" customHeight="1"/>
     <row r="29" ht="45" customHeight="1"/>
@@ -2075,7 +2079,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B6 F6 B7 F7 B11"/>
   </dataValidations>
   <pageMargins left="0.804166666666667" right="0.804166666666667" top="0.804166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
-  <pageSetup paperSize="9" scale="53" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -1526,10 +1526,10 @@
   <cols>
     <col min="1" max="1" width="30.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="36.375" style="2" customWidth="1"/>
     <col min="10" max="17" width="9" style="3"/>
   </cols>
@@ -2079,7 +2079,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B6 F6 B7 F7 B11"/>
   </dataValidations>
   <pageMargins left="0.804166666666667" right="0.804166666666667" top="0.804166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
-  <pageSetup paperSize="9" scale="51" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="41" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23775" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="1.费用报销单" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>费用报销单</t>
   </si>
@@ -174,9 +174,6 @@
   </si>
   <si>
     <t>报销人：{expSign}</t>
-  </si>
-  <si>
-    <t>裁切线</t>
   </si>
   <si>
     <t>成本一览表</t>
@@ -634,7 +631,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -754,15 +751,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="dashed">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -889,7 +877,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -901,34 +889,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1133,7 +1121,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1741,9 +1729,7 @@
       <c r="Q8" s="38"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:17">
-      <c r="A9" s="31" t="s">
-        <v>36</v>
-      </c>
+      <c r="A9" s="31"/>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
@@ -1762,7 +1748,7 @@
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:16">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1808,7 +1794,7 @@
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:16">
       <c r="A12" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>6</v>
@@ -1817,10 +1803,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>40</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>9</v>
@@ -1837,22 +1823,22 @@
     </row>
     <row r="13" ht="35.1" customHeight="1" spans="1:16">
       <c r="A13" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="C13" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="D13" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="F13" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>46</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="37"/>
@@ -1869,19 +1855,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="D14" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="E14" s="35" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" ht="35.1" customHeight="1" spans="1:6">
@@ -2076,7 +2062,7 @@
     <mergeCell ref="J27:P27"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B6 F6 B7 F7 B11"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B11 B6:B7 F6:F7"/>
   </dataValidations>
   <pageMargins left="0.804166666666667" right="0.804166666666667" top="0.804166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
   <pageSetup paperSize="9" scale="41" orientation="portrait"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -10,7 +10,7 @@
     <sheet name="1.费用报销单" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1.费用报销单'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1.费用报销单'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="20"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -47,7 +47,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="20"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -59,7 +59,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="20"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -68,7 +68,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="20"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -254,20 +254,20 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1001,12 +1001,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1015,134 +1018,123 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="7" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1217,11 +1209,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>635</xdr:colOff>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>43815</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="588010"/>
+    <xdr:ext cx="2143125" cy="968375"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="图片 1"/>
@@ -1235,8 +1227,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="635" y="43815"/>
-          <a:ext cx="2000250" cy="588010"/>
+          <a:off x="9525" y="43815"/>
+          <a:ext cx="2143125" cy="968375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1509,528 +1501,752 @@
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="36.375" style="2" customWidth="1"/>
-    <col min="10" max="17" width="9" style="3"/>
+    <col min="1" max="1" width="31" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="36.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="36.375" style="3" customWidth="1"/>
+    <col min="10" max="17" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="84" customHeight="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" ht="84" customHeight="1" spans="1:17">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="2" ht="35.1" customHeight="1" spans="1:17">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-    </row>
-    <row r="3" ht="35.1" customHeight="1" spans="1:17">
-      <c r="A3" s="11" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-    </row>
-    <row r="4" ht="45" customHeight="1" spans="1:17">
-      <c r="A4" s="15" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="15" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-    </row>
-    <row r="5" ht="45" customHeight="1" spans="1:17">
-      <c r="A5" s="18" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-    </row>
-    <row r="6" ht="45" customHeight="1" spans="1:17">
-      <c r="A6" s="24" t="s">
+      <c r="F10" s="23"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B11" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C11" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F11" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" spans="1:17">
-      <c r="A7" s="24" t="s">
+      <c r="G11" s="1"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A12" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B12" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C12" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-    </row>
-    <row r="8" ht="45" customHeight="1" spans="1:17">
-      <c r="A8" s="28" t="s">
+      <c r="G12" s="1"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+    </row>
+    <row r="13" ht="45" customHeight="1" spans="1:17">
+      <c r="A13" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C13" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D13" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E13" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F13" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-    </row>
-    <row r="9" ht="45" customHeight="1" spans="1:17">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-    </row>
-    <row r="10" ht="45" customHeight="1" spans="1:16">
-      <c r="A10" s="4" t="s">
+      <c r="H13" s="30"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+    </row>
+    <row r="14" ht="45" customHeight="1" spans="1:17">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:17">
+      <c r="A15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-    </row>
-    <row r="11" ht="35.1" customHeight="1" spans="1:16">
-      <c r="A11" s="5" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-    </row>
-    <row r="12" ht="35.1" customHeight="1" spans="1:16">
-      <c r="A12" s="24" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A17" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F17" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-    </row>
-    <row r="13" ht="35.1" customHeight="1" spans="1:16">
-      <c r="A13" s="15" t="s">
+      <c r="G17" s="1"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A18" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C18" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F18" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-    </row>
-    <row r="14" ht="35.1" customHeight="1" spans="1:6">
-      <c r="A14" s="33" t="s">
+      <c r="G18" s="1"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A23" s="24"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="A24" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B24" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C24" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D24" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E24" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F24" s="35" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" ht="35.1" customHeight="1" spans="1:6">
-      <c r="A15" s="28" t="s">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+    </row>
+    <row r="25" ht="35.1" customHeight="1" spans="1:6">
+      <c r="A25" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B25" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C25" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D25" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E25" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="F25" s="29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" ht="50.1" customHeight="1"/>
-    <row r="17" ht="54.95" customHeight="1" spans="8:17">
-      <c r="H17" s="10"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-    </row>
-    <row r="18" ht="39" customHeight="1" spans="8:17">
-      <c r="H18" s="10"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-    </row>
-    <row r="19" ht="35.1" customHeight="1" spans="8:17">
-      <c r="H19" s="10"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="8:17">
-      <c r="H20" s="10"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="8:17">
-      <c r="H21" s="10"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="8:17">
-      <c r="H22" s="10"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="8:17">
-      <c r="H23" s="10"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-    </row>
-    <row r="24" ht="45" hidden="1" customHeight="1" spans="8:17">
-      <c r="H24" s="10"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="38"/>
-    </row>
-    <row r="25" ht="45" hidden="1" customHeight="1" spans="8:17">
-      <c r="H25" s="10"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="8:17">
-      <c r="H26" s="10"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="8:17">
-      <c r="H27" s="10"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="38"/>
-    </row>
-    <row r="28" ht="45" customHeight="1"/>
-    <row r="29" ht="45" customHeight="1"/>
-    <row r="30" ht="35.1" customHeight="1" spans="8:8">
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" ht="29.1" customHeight="1"/>
+    <row r="26" ht="50.1" customHeight="1"/>
+    <row r="27" ht="54.95" customHeight="1" spans="8:17">
+      <c r="H27" s="30"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+    </row>
+    <row r="28" ht="39" customHeight="1" spans="8:17">
+      <c r="H28" s="30"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+    </row>
+    <row r="29" ht="35.1" customHeight="1" spans="8:17">
+      <c r="H29" s="30"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="37"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="37"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="8:17">
+      <c r="H30" s="30"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="37"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="37"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="8:17">
+      <c r="H31" s="30"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
+      <c r="N31" s="37"/>
+      <c r="O31" s="37"/>
+      <c r="P31" s="37"/>
+      <c r="Q31" s="37"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="8:17">
+      <c r="H32" s="30"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="37"/>
+      <c r="N32" s="37"/>
+      <c r="O32" s="37"/>
+      <c r="P32" s="37"/>
+      <c r="Q32" s="37"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="8:17">
+      <c r="H33" s="30"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="37"/>
+      <c r="N33" s="37"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="37"/>
+    </row>
+    <row r="34" ht="45" hidden="1" customHeight="1" spans="8:17">
+      <c r="H34" s="30"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+    </row>
+    <row r="35" ht="45" hidden="1" customHeight="1" spans="8:17">
+      <c r="H35" s="30"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="37"/>
+      <c r="N35" s="37"/>
+      <c r="O35" s="37"/>
+      <c r="P35" s="37"/>
+      <c r="Q35" s="37"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="8:17">
+      <c r="H36" s="30"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37"/>
+      <c r="M36" s="37"/>
+      <c r="N36" s="37"/>
+      <c r="O36" s="37"/>
+      <c r="P36" s="37"/>
+      <c r="Q36" s="37"/>
+    </row>
+    <row r="37" ht="45" customHeight="1" spans="8:17">
+      <c r="H37" s="30"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="37"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="37"/>
+      <c r="O37" s="37"/>
+      <c r="P37" s="37"/>
+      <c r="Q37" s="37"/>
+    </row>
+    <row r="38" ht="45" customHeight="1"/>
+    <row r="39" ht="45" customHeight="1"/>
+    <row r="40" ht="35.1" customHeight="1" spans="8:8">
+      <c r="H40" s="30"/>
+    </row>
+    <row r="41" ht="29.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="39">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="J2:Q2"/>
@@ -2038,34 +2254,44 @@
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B5:D5"/>
     <mergeCell ref="J5:Q5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="J6:Q6"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="J7:Q7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="J8:Q8"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="J9:Q9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="J17:Q17"/>
-    <mergeCell ref="J18:Q18"/>
-    <mergeCell ref="J19:Q19"/>
-    <mergeCell ref="J20:Q20"/>
-    <mergeCell ref="J21:Q21"/>
-    <mergeCell ref="J22:Q22"/>
-    <mergeCell ref="J23:Q23"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="J10:Q10"/>
+    <mergeCell ref="J11:Q11"/>
+    <mergeCell ref="J12:Q12"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="J14:Q14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="J27:Q27"/>
+    <mergeCell ref="J28:Q28"/>
+    <mergeCell ref="J29:Q29"/>
+    <mergeCell ref="J30:Q30"/>
+    <mergeCell ref="J31:Q31"/>
+    <mergeCell ref="J32:Q32"/>
+    <mergeCell ref="J33:Q33"/>
+    <mergeCell ref="J36:P36"/>
+    <mergeCell ref="J37:P37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B11 B6:B7 F6:F7"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B16 B11:B12 F11:F12"/>
   </dataValidations>
-  <pageMargins left="0.804166666666667" right="0.804166666666667" top="0.804166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
-  <pageSetup paperSize="9" scale="41" orientation="portrait"/>
+  <pageMargins left="0.747916666666667" right="0.196527777777778" top="0.354166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" scale="43" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -10,7 +10,7 @@
     <sheet name="1.费用报销单" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1.费用报销单'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1.费用报销单'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,19 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>费用报销单</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>单位：</t>
     </r>
     <r>
@@ -56,25 +49,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>部门：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{dept}</t>
-    </r>
+    <t>部门：</t>
+  </si>
+  <si>
+    <t>{dept}</t>
   </si>
   <si>
     <t>{yearMonthDay}</t>
@@ -164,7 +142,7 @@
     <t>财务负责人：</t>
   </si>
   <si>
-    <t>会计：</t>
+    <t xml:space="preserve">  会计：</t>
   </si>
   <si>
     <t>出纳：</t>
@@ -637,15 +615,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -717,6 +686,15 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1001,7 +979,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1021,7 +999,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1033,16 +1011,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1056,52 +1039,52 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1111,37 +1094,63 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1501,20 +1510,21 @@
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="36.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="29.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="36.375" style="3" customWidth="1"/>
-    <col min="10" max="17" width="9" style="4"/>
+    <col min="1" max="1" width="29.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="29.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="36.375" style="3" customWidth="1"/>
+    <col min="11" max="18" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="84" customHeight="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1523,10 +1533,10 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
-      <c r="G1" s="1"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="3"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1534,333 +1544,349 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="R1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
-      <c r="A3" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>6</v>
       </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A3" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="B3" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="13"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
       <c r="F3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="G3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A4" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="18"/>
       <c r="F4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="G4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A5" s="16"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="G5" s="16"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="16"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="G6" s="16"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A7" s="16"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="G7" s="16"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A8" s="16"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="16"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="G8" s="16"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
-      <c r="A10" s="12" t="s">
-        <v>14</v>
+      <c r="G9" s="16"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A10" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="20"/>
-      <c r="D10" s="21" t="s">
-        <v>16</v>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
-      <c r="A11" s="24" t="s">
+      <c r="F10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="G10" s="24"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A11" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="B11" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="C11" s="27"/>
+      <c r="D11" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
-      <c r="A12" s="24" t="s">
+      <c r="G11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="H11" s="1"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A12" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="B12" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-    </row>
-    <row r="13" ht="45" customHeight="1" spans="1:17">
-      <c r="A13" s="27" t="s">
+      <c r="G12" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="H12" s="1"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+    </row>
+    <row r="13" ht="45" customHeight="1" spans="1:18">
+      <c r="A13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="B13" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="C13" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="D13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="E13" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-    </row>
-    <row r="14" ht="45" customHeight="1" spans="1:17">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:17">
+      <c r="F13" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="33"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+    </row>
+    <row r="14" ht="45" customHeight="1" spans="1:18">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
       <c r="A15" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="J15" s="3"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1868,109 +1894,115 @@
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="R15" s="4"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A16" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
-      <c r="A17" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="12" t="s">
+      <c r="G16" s="10" t="s">
         <v>6</v>
       </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A17" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C17" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="25" t="s">
         <v>39</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+        <v>40</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A18" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>43</v>
       </c>
+      <c r="D18" s="17"/>
       <c r="E18" s="16" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="G18" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="16"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="17"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="16"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="4"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="3"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1978,18 +2010,19 @@
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="R19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="16"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="27"/>
       <c r="E20" s="16"/>
       <c r="F20" s="16"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="16"/>
       <c r="H20" s="1"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="4"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="3"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -1997,18 +2030,19 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="R20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="27"/>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="16"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="4"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="3"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2016,18 +2050,19 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="R21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="27"/>
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="16"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="4"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="3"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2035,49 +2070,51 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
-      <c r="A23" s="24"/>
-      <c r="B23" s="12"/>
+      <c r="R22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A23" s="25"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="15"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:17">
-      <c r="A24" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="24" t="s">
+      <c r="G23" s="15"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A24" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="C24" s="38"/>
+      <c r="D24" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="35" t="s">
+      <c r="E24" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="F24" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>50</v>
+      </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="4"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="3"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2085,213 +2122,227 @@
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
-    </row>
-    <row r="25" ht="35.1" customHeight="1" spans="1:6">
-      <c r="A25" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="28" t="s">
+      <c r="R24" s="4"/>
+    </row>
+    <row r="25" ht="35.1" customHeight="1" spans="1:7">
+      <c r="A25" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="B25" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="C25" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="D25" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="E25" s="32" t="s">
         <v>35</v>
       </c>
+      <c r="F25" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" ht="50.1" customHeight="1"/>
-    <row r="27" ht="54.95" customHeight="1" spans="8:17">
-      <c r="H27" s="30"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-    </row>
-    <row r="28" ht="39" customHeight="1" spans="8:17">
-      <c r="H28" s="30"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
-      <c r="Q28" s="37"/>
-    </row>
-    <row r="29" ht="35.1" customHeight="1" spans="8:17">
-      <c r="H29" s="30"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="37"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="8:17">
-      <c r="H30" s="30"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
-      <c r="N30" s="37"/>
-      <c r="O30" s="37"/>
-      <c r="P30" s="37"/>
-      <c r="Q30" s="37"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="8:17">
-      <c r="H31" s="30"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="37"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="8:17">
-      <c r="H32" s="30"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="37"/>
-      <c r="P32" s="37"/>
-      <c r="Q32" s="37"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="8:17">
-      <c r="H33" s="30"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="37"/>
-      <c r="N33" s="37"/>
-      <c r="O33" s="37"/>
-      <c r="P33" s="37"/>
-      <c r="Q33" s="37"/>
-    </row>
-    <row r="34" ht="45" hidden="1" customHeight="1" spans="8:17">
-      <c r="H34" s="30"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37"/>
-      <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-      <c r="P34" s="37"/>
-      <c r="Q34" s="37"/>
-    </row>
-    <row r="35" ht="45" hidden="1" customHeight="1" spans="8:17">
-      <c r="H35" s="30"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="37"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="8:17">
-      <c r="H36" s="30"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="37"/>
-      <c r="L36" s="37"/>
-      <c r="M36" s="37"/>
-      <c r="N36" s="37"/>
-      <c r="O36" s="37"/>
-      <c r="P36" s="37"/>
-      <c r="Q36" s="37"/>
-    </row>
-    <row r="37" ht="45" customHeight="1" spans="8:17">
-      <c r="H37" s="30"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="37"/>
+    <row r="27" ht="54.95" customHeight="1" spans="9:18">
+      <c r="I27" s="45"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="44"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+    </row>
+    <row r="28" ht="39" customHeight="1" spans="9:18">
+      <c r="I28" s="45"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+    </row>
+    <row r="29" ht="35.1" customHeight="1" spans="9:18">
+      <c r="I29" s="45"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="9:18">
+      <c r="I30" s="45"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="9:18">
+      <c r="I31" s="45"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="9:18">
+      <c r="I32" s="45"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="9:18">
+      <c r="I33" s="45"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+    </row>
+    <row r="34" ht="45" hidden="1" customHeight="1" spans="9:18">
+      <c r="I34" s="45"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+    </row>
+    <row r="35" ht="45" hidden="1" customHeight="1" spans="9:18">
+      <c r="I35" s="45"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="44"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="44"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="9:18">
+      <c r="I36" s="45"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="44"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="44"/>
+      <c r="P36" s="44"/>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="44"/>
+    </row>
+    <row r="37" ht="45" customHeight="1" spans="9:18">
+      <c r="I37" s="45"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="44"/>
     </row>
     <row r="38" ht="45" customHeight="1"/>
     <row r="39" ht="45" customHeight="1"/>
-    <row r="40" ht="35.1" customHeight="1" spans="8:8">
-      <c r="H40" s="30"/>
+    <row r="40" ht="35.1" customHeight="1" spans="9:9">
+      <c r="I40" s="45"/>
     </row>
     <row r="41" ht="29.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="J6:Q6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="J7:Q7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="J8:Q8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="J9:Q9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="J10:Q10"/>
-    <mergeCell ref="J11:Q11"/>
-    <mergeCell ref="J12:Q12"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="J14:Q14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="J27:Q27"/>
-    <mergeCell ref="J28:Q28"/>
-    <mergeCell ref="J29:Q29"/>
-    <mergeCell ref="J30:Q30"/>
-    <mergeCell ref="J31:Q31"/>
-    <mergeCell ref="J32:Q32"/>
-    <mergeCell ref="J33:Q33"/>
-    <mergeCell ref="J36:P36"/>
-    <mergeCell ref="J37:P37"/>
+  <mergeCells count="51">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="K2:R2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="K3:R3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="K4:R4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="K5:R5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="K6:R6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="K16:Q16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="K17:Q17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="K18:Q18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="K27:R27"/>
+    <mergeCell ref="K28:R28"/>
+    <mergeCell ref="K29:R29"/>
+    <mergeCell ref="K30:R30"/>
+    <mergeCell ref="K31:R31"/>
+    <mergeCell ref="K32:R32"/>
+    <mergeCell ref="K33:R33"/>
+    <mergeCell ref="K36:Q36"/>
+    <mergeCell ref="K37:Q37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B16 B11:B12 F11:F12"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 C2 B11 B12 B16 C16 G11:G12"/>
   </dataValidations>
   <pageMargins left="0.747916666666667" right="0.196527777777778" top="0.354166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
-  <pageSetup paperSize="9" scale="43" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="41" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -36,6 +36,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>单位：</t>
     </r>
     <r>
@@ -979,7 +986,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1008,6 +1015,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1016,11 +1027,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1105,19 +1112,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1557,29 +1556,29 @@
       <c r="D2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="12" t="s">
@@ -1595,16 +1594,16 @@
         <v>10</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A4" s="16" t="s">
@@ -1623,16 +1622,16 @@
         <v>14</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A5" s="16"/>
@@ -1643,16 +1642,16 @@
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A6" s="16"/>
@@ -1663,16 +1662,16 @@
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A7" s="16"/>
@@ -1683,16 +1682,16 @@
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A8" s="16"/>
@@ -1703,16 +1702,16 @@
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A9" s="16"/>
@@ -1723,19 +1722,19 @@
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -1751,16 +1750,16 @@
       </c>
       <c r="G10" s="24"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A11" s="25" t="s">
@@ -1783,16 +1782,16 @@
         <v>24</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A12" s="25" t="s">
@@ -1815,16 +1814,16 @@
         <v>30</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
     </row>
     <row r="13" ht="45" customHeight="1" spans="1:18">
       <c r="A13" s="28" t="s">
@@ -1842,39 +1841,39 @@
       <c r="E13" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="33" t="s">
+      <c r="F13" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="33"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-    </row>
-    <row r="14" ht="45" customHeight="1" spans="1:18">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="44"/>
-      <c r="P14" s="44"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="44"/>
+      <c r="G13" s="32"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+    </row>
+    <row r="14" ht="188" customHeight="1" spans="1:18">
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
       <c r="A15" s="5" t="s">
@@ -1907,32 +1906,32 @@
       <c r="D16" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="44"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
       <c r="R16" s="4"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A17" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="12" t="s">
@@ -1949,15 +1948,15 @@
         <v>10</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="44"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
       <c r="R17" s="4"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
@@ -1981,21 +1980,21 @@
         <v>46</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
       <c r="R18" s="4"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
-      <c r="C19" s="35"/>
+      <c r="C19" s="34"/>
       <c r="D19" s="17"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
@@ -2074,42 +2073,42 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A23" s="25"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="13"/>
       <c r="E23" s="25"/>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
       <c r="R23" s="4"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A24" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="38"/>
+      <c r="C24" s="36"/>
       <c r="D24" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="41" t="s">
+      <c r="G24" s="39" t="s">
         <v>50</v>
       </c>
       <c r="H24" s="1"/>
@@ -2140,148 +2139,148 @@
       <c r="E25" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="33"/>
+      <c r="G25" s="32"/>
     </row>
     <row r="26" ht="50.1" customHeight="1"/>
     <row r="27" ht="54.95" customHeight="1" spans="9:18">
-      <c r="I27" s="45"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" ht="39" customHeight="1" spans="9:18">
-      <c r="I28" s="45"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" ht="35.1" customHeight="1" spans="9:18">
-      <c r="I29" s="45"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="9:18">
-      <c r="I30" s="45"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="9:18">
-      <c r="I31" s="45"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="42"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="9:18">
-      <c r="I32" s="45"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="44"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="9:18">
-      <c r="I33" s="45"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="44"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="44"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" ht="45" hidden="1" customHeight="1" spans="9:18">
-      <c r="I34" s="45"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="44"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" ht="45" hidden="1" customHeight="1" spans="9:18">
-      <c r="I35" s="45"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="44"/>
-      <c r="L35" s="44"/>
-      <c r="M35" s="44"/>
-      <c r="N35" s="44"/>
-      <c r="O35" s="44"/>
-      <c r="P35" s="44"/>
-      <c r="Q35" s="44"/>
-      <c r="R35" s="44"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42"/>
+      <c r="O35" s="42"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="9:18">
-      <c r="I36" s="45"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="44"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="44"/>
-      <c r="N36" s="44"/>
-      <c r="O36" s="44"/>
-      <c r="P36" s="44"/>
-      <c r="Q36" s="44"/>
-      <c r="R36" s="44"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" ht="45" customHeight="1" spans="9:18">
-      <c r="I37" s="45"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="44"/>
-      <c r="L37" s="44"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="44"/>
-      <c r="R37" s="44"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="42"/>
+      <c r="N37" s="42"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" ht="45" customHeight="1"/>
     <row r="39" ht="45" customHeight="1"/>
     <row r="40" ht="35.1" customHeight="1" spans="9:9">
-      <c r="I40" s="45"/>
+      <c r="I40" s="43"/>
     </row>
     <row r="41" ht="29.1" customHeight="1"/>
   </sheetData>
@@ -2339,7 +2338,7 @@
     <mergeCell ref="K37:Q37"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 C2 B11 B12 B16 C16 G11:G12"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C2 B16:C16 B11:B12 G11:G12"/>
   </dataValidations>
   <pageMargins left="0.747916666666667" right="0.196527777777778" top="0.354166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
   <pageSetup paperSize="9" scale="41" orientation="portrait"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>费用报销单</t>
   </si>
@@ -143,19 +143,7 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t>总经理：</t>
-  </si>
-  <si>
-    <t>财务负责人：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  会计：</t>
-  </si>
-  <si>
-    <t>出纳：</t>
-  </si>
-  <si>
-    <t>部门负责人：</t>
+    <t>总经理：      财务负责人：     会计：     出纳：     部门负责人：      分管领导：</t>
   </si>
   <si>
     <t>报销人：{expSign}</t>
@@ -986,7 +974,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1094,18 +1082,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1566,16 +1544,16 @@
         <v>6</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A3" s="12" t="s">
@@ -1594,16 +1572,16 @@
         <v>10</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A4" s="16" t="s">
@@ -1622,16 +1600,16 @@
         <v>14</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A5" s="16"/>
@@ -1642,16 +1620,16 @@
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A6" s="16"/>
@@ -1662,16 +1640,16 @@
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A7" s="16"/>
@@ -1682,16 +1660,16 @@
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A8" s="16"/>
@@ -1702,16 +1680,16 @@
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="42"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A9" s="16"/>
@@ -1722,16 +1700,16 @@
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A10" s="12" t="s">
@@ -1750,16 +1728,16 @@
       </c>
       <c r="G10" s="24"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A11" s="25" t="s">
@@ -1782,16 +1760,16 @@
         <v>24</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="42"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A12" s="25" t="s">
@@ -1814,70 +1792,62 @@
         <v>30</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
     </row>
     <row r="13" ht="45" customHeight="1" spans="1:18">
       <c r="A13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="32"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
+      <c r="G13" s="29"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
     </row>
     <row r="14" ht="188" customHeight="1" spans="1:18">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1916,20 +1886,20 @@
         <v>6</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
       <c r="R16" s="4"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A17" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>7</v>
@@ -1939,62 +1909,62 @@
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
       <c r="R17" s="4"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A18" s="16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
       <c r="R18" s="4"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
-      <c r="C19" s="34"/>
+      <c r="C19" s="31"/>
       <c r="D19" s="17"/>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
@@ -2080,36 +2050,36 @@
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
       <c r="R23" s="4"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
       <c r="A24" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="36"/>
+      <c r="B24" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="33"/>
       <c r="D24" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="39" t="s">
-        <v>50</v>
+      <c r="G24" s="36" t="s">
+        <v>46</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -2127,164 +2097,156 @@
       <c r="A25" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="32"/>
+      <c r="G25" s="29"/>
     </row>
     <row r="26" ht="50.1" customHeight="1"/>
     <row r="27" ht="54.95" customHeight="1" spans="9:18">
-      <c r="I27" s="43"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="42"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="39"/>
     </row>
     <row r="28" ht="39" customHeight="1" spans="9:18">
-      <c r="I28" s="43"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
     </row>
     <row r="29" ht="35.1" customHeight="1" spans="9:18">
-      <c r="I29" s="43"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="9:18">
-      <c r="I30" s="43"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="39"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="9:18">
-      <c r="I31" s="43"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="9:18">
-      <c r="I32" s="43"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="42"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
+      <c r="Q32" s="39"/>
+      <c r="R32" s="39"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="9:18">
-      <c r="I33" s="43"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="42"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="39"/>
+      <c r="R33" s="39"/>
     </row>
     <row r="34" ht="45" hidden="1" customHeight="1" spans="9:18">
-      <c r="I34" s="43"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="42"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="39"/>
+      <c r="R34" s="39"/>
     </row>
     <row r="35" ht="45" hidden="1" customHeight="1" spans="9:18">
-      <c r="I35" s="43"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="42"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="39"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="9:18">
-      <c r="I36" s="43"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="42"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
+      <c r="R36" s="39"/>
     </row>
     <row r="37" ht="45" customHeight="1" spans="9:18">
-      <c r="I37" s="43"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="42"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42"/>
-      <c r="N37" s="42"/>
-      <c r="O37" s="42"/>
-      <c r="P37" s="42"/>
-      <c r="Q37" s="42"/>
-      <c r="R37" s="42"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="39"/>
+      <c r="R37" s="39"/>
     </row>
     <row r="38" ht="45" customHeight="1"/>
     <row r="39" ht="45" customHeight="1"/>
     <row r="40" ht="35.1" customHeight="1" spans="9:9">
-      <c r="I40" s="43"/>
+      <c r="I40" s="40"/>
     </row>
     <row r="41" ht="29.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="53">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:R2"/>
@@ -2309,6 +2271,7 @@
     <mergeCell ref="K11:R11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="K12:R12"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="K14:R14"/>
@@ -2326,6 +2289,7 @@
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="K23:Q23"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="K27:R27"/>
     <mergeCell ref="K28:R28"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -143,7 +143,7 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t>总经理：      财务负责人：     会计：     出纳：     部门负责人：      分管领导：</t>
+    <t xml:space="preserve">总经理：      财务负责人：     会计：     出纳：       分管领导：      部门负责人：      </t>
   </si>
   <si>
     <t>报销人：{expSign}</t>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -29,8 +29,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+100字</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>费用报销单</t>
   </si>
@@ -56,10 +88,7 @@
     </r>
   </si>
   <si>
-    <t>部门：</t>
-  </si>
-  <si>
-    <t>{dept}</t>
+    <t>部门：{dept}</t>
   </si>
   <si>
     <t>{yearMonthDay}</t>
@@ -143,10 +172,10 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t xml:space="preserve">总经理：      财务负责人：     会计：     出纳：       分管领导：      部门负责人：      </t>
-  </si>
-  <si>
-    <t>报销人：{expSign}</t>
+    <t>审批：          审核：          复核：       出纳：        分管领导：        部门负责人：         报销人：</t>
+  </si>
+  <si>
+    <t>{expSign}</t>
   </si>
   <si>
     <t>成本一览表</t>
@@ -205,7 +234,7 @@
     <numFmt numFmtId="177" formatCode="[DBNum2][$RMB]General;[Red][DBNum2][$RMB]General"/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -409,6 +438,17 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -604,7 +644,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -718,15 +758,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -850,7 +881,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -862,34 +893,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -974,7 +1005,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -984,6 +1015,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -994,15 +1028,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1022,7 +1060,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1042,6 +1080,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1050,11 +1092,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1078,7 +1120,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1086,15 +1136,23 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1102,7 +1160,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1490,763 +1548,759 @@
   <dimension ref="A1:R41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="29.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="28.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="29.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="29.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="36.375" style="3" customWidth="1"/>
-    <col min="11" max="18" width="9" style="4"/>
+    <col min="1" max="1" width="26.8333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.6" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.4916666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3583333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="21.3166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.1" style="2" customWidth="1"/>
+    <col min="10" max="10" width="36.375" style="4" customWidth="1"/>
+    <col min="11" max="18" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15" t="s">
+      <c r="G3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="1"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A4" s="16" t="s">
+      <c r="B4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="1"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="39"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A10" s="12" t="s">
+      <c r="B10" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22" t="s">
+      <c r="F10" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="G10" s="27"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A11" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A11" s="25" t="s">
+      <c r="B11" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="C11" s="30"/>
+      <c r="D11" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="25" t="s">
+      <c r="E11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="F11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="G11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="H11" s="1"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
+      <c r="A12" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A12" s="25" t="s">
+      <c r="B12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="25" t="s">
+      <c r="E12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="F12" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="G12" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="H12" s="1"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+    </row>
+    <row r="13" ht="70" customHeight="1" spans="1:18">
+      <c r="A13" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-    </row>
-    <row r="13" ht="45" customHeight="1" spans="1:18">
-      <c r="A13" s="28" t="s">
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="29" t="s">
+      <c r="I13" s="47"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+    </row>
+    <row r="14" ht="140" customHeight="1" spans="1:18">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
+      <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="29"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-    </row>
-    <row r="14" ht="188" customHeight="1" spans="1:18">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="50" customHeight="1" spans="1:18">
+      <c r="A16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="5"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="57" customHeight="1" spans="1:18">
+      <c r="A17" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A16" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="11" t="s">
+      <c r="B17" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A17" s="25" t="s">
+      <c r="C17" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="25" t="s">
+      <c r="F17" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="G17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="5"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
+      <c r="A18" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="39"/>
-      <c r="R17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A18" s="16" t="s">
+      <c r="B18" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="C18" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="20"/>
+      <c r="E18" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="16" t="s">
+      <c r="F18" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="G18" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="5"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A23" s="25"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
+      <c r="A23" s="28"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A24" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="32" t="s">
+      <c r="I23" s="44"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
+      <c r="O23" s="46"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="5"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="52" customHeight="1" spans="1:18">
+      <c r="A24" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="40"/>
+      <c r="D24" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="25" t="s">
+      <c r="E24" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="34" t="s">
+      <c r="F24" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="43" t="s">
         <v>45</v>
-      </c>
-      <c r="F24" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="36" t="s">
-        <v>46</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-    </row>
-    <row r="25" ht="35.1" customHeight="1" spans="1:7">
-      <c r="A25" s="28" t="s">
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+    </row>
+    <row r="25" ht="73" customHeight="1" spans="1:7">
+      <c r="A25" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" s="29"/>
     </row>
     <row r="26" ht="50.1" customHeight="1"/>
     <row r="27" ht="54.95" customHeight="1" spans="9:18">
-      <c r="I27" s="40"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="39"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
     </row>
     <row r="28" ht="39" customHeight="1" spans="9:18">
-      <c r="I28" s="40"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="46"/>
     </row>
     <row r="29" ht="35.1" customHeight="1" spans="9:18">
-      <c r="I29" s="40"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="46"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="9:18">
-      <c r="I30" s="40"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="46"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="9:18">
-      <c r="I31" s="40"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="9:18">
-      <c r="I32" s="40"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="39"/>
-      <c r="Q32" s="39"/>
-      <c r="R32" s="39"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="46"/>
+      <c r="Q32" s="46"/>
+      <c r="R32" s="46"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="9:18">
-      <c r="I33" s="40"/>
-      <c r="J33" s="38"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="39"/>
-      <c r="Q33" s="39"/>
-      <c r="R33" s="39"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="46"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="46"/>
     </row>
     <row r="34" ht="45" hidden="1" customHeight="1" spans="9:18">
-      <c r="I34" s="40"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="39"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="46"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="46"/>
     </row>
     <row r="35" ht="45" hidden="1" customHeight="1" spans="9:18">
-      <c r="I35" s="40"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="39"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="46"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="46"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="9:18">
-      <c r="I36" s="40"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="39"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="46"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="46"/>
     </row>
     <row r="37" ht="45" customHeight="1" spans="9:18">
-      <c r="I37" s="40"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="39"/>
-      <c r="Q37" s="39"/>
-      <c r="R37" s="39"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="46"/>
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
     </row>
     <row r="38" ht="45" customHeight="1"/>
     <row r="39" ht="45" customHeight="1"/>
     <row r="40" ht="35.1" customHeight="1" spans="9:9">
-      <c r="I40" s="40"/>
+      <c r="I40" s="47"/>
     </row>
     <row r="41" ht="29.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="51">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:R2"/>
@@ -2271,8 +2325,7 @@
     <mergeCell ref="K11:R11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="K12:R12"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="K14:R14"/>
     <mergeCell ref="A15:G15"/>
@@ -2289,8 +2342,7 @@
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="K23:Q23"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A25:F25"/>
     <mergeCell ref="K27:R27"/>
     <mergeCell ref="K28:R28"/>
     <mergeCell ref="K29:R29"/>
@@ -2304,9 +2356,10 @@
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C2 B16:C16 B11:B12 G11:G12"/>
   </dataValidations>
-  <pageMargins left="0.747916666666667" right="0.196527777777778" top="0.354166666666667" bottom="0.804166666666667" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageMargins left="0.314583333333333" right="0.118055555555556" top="0.354166666666667" bottom="0.196527777777778" header="0.298611111111111" footer="0.298611111111111"/>
   <pageSetup paperSize="9" scale="41" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -88,7 +88,25 @@
     </r>
   </si>
   <si>
-    <t>部门：{dept}</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>部门：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{dept}</t>
+    </r>
   </si>
   <si>
     <t>{yearMonthDay}</t>
@@ -124,13 +142,15 @@
     <t>{data1.memo}</t>
   </si>
   <si>
-    <t xml:space="preserve">总计金额（大写）                   </t>
+    <t xml:space="preserve">总计金额
+（大写）                   </t>
   </si>
   <si>
     <t>{upFeeTotal}</t>
   </si>
   <si>
-    <t>总计金额（小写）</t>
+    <t>总计金额
+（小写）</t>
   </si>
   <si>
     <t>￥{lowFeeTotalQian}</t>
@@ -181,7 +201,7 @@
     <t>成本一览表</t>
   </si>
   <si>
-    <t>项目/合同名称</t>
+    <t>编号合同名称</t>
   </si>
   <si>
     <t>金额（含税）</t>
@@ -190,7 +210,7 @@
     <t>进项税额</t>
   </si>
   <si>
-    <t>{data2.prjName}</t>
+    <t>{data2.prjNameNo}</t>
   </si>
   <si>
     <t>{data2.item}</t>
@@ -1037,11 +1057,11 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1552,7 +1572,7 @@
     <col min="2" max="2" width="22.6" style="2" customWidth="1"/>
     <col min="3" max="3" width="37.4916666666667" style="3" customWidth="1"/>
     <col min="4" max="4" width="50.3583333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="21.3166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.8333333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="26" style="2" customWidth="1"/>
     <col min="7" max="7" width="26.1" style="2" customWidth="1"/>
     <col min="10" max="10" width="36.375" style="4" customWidth="1"/>
@@ -1882,7 +1902,7 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="46"/>
     </row>
-    <row r="14" ht="140" customHeight="1" spans="1:18">
+    <row r="14" ht="90" customHeight="1" spans="1:18">
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="35"/>
@@ -1901,7 +1921,7 @@
       <c r="Q14" s="46"/>
       <c r="R14" s="46"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="84" customHeight="1" spans="1:18">
+    <row r="15" s="1" customFormat="1" ht="90" customHeight="1" spans="1:18">
       <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
@@ -2115,7 +2135,7 @@
       <c r="Q23" s="46"/>
       <c r="R23" s="5"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="52" customHeight="1" spans="1:18">
+    <row r="24" s="1" customFormat="1" ht="77" customHeight="1" spans="1:18">
       <c r="A24" s="28" t="s">
         <v>14</v>
       </c>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -62,51 +62,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>费用报销单</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单位：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{unit}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>部门：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{dept}</t>
-    </r>
+    <t>单位：</t>
+  </si>
+  <si>
+    <t>{unit}</t>
+  </si>
+  <si>
+    <t>部门：</t>
+  </si>
+  <si>
+    <t>{dept}</t>
   </si>
   <si>
     <t>{yearMonthDay}</t>
@@ -192,10 +162,10 @@
     <t>{devSubject}</t>
   </si>
   <si>
-    <t>审批：          审核：          复核：       出纳：        分管领导：        部门负责人：         报销人：</t>
-  </si>
-  <si>
-    <t>{expSign}</t>
+    <t xml:space="preserve">审批：           审核：           复核：         出纳：          分管领导：          部门负责人：         </t>
+  </si>
+  <si>
+    <t>报销人：{expSign}</t>
   </si>
   <si>
     <t>成本一览表</t>
@@ -1056,12 +1026,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1150,10 +1124,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1569,10 +1539,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.8333333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.6" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.4916666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3583333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.8333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="39.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="62.25" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27" style="2" customWidth="1"/>
     <col min="6" max="6" width="26" style="2" customWidth="1"/>
     <col min="7" max="7" width="26.1" style="2" customWidth="1"/>
     <col min="10" max="10" width="36.375" style="4" customWidth="1"/>
@@ -1605,19 +1575,23 @@
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="44"/>
@@ -1632,20 +1606,20 @@
       <c r="R2" s="46"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17" t="s">
+      <c r="A3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>9</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>11</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="44"/>
@@ -1660,20 +1634,20 @@
       <c r="R3" s="46"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A4" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>13</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="44"/>
@@ -1688,13 +1662,13 @@
       <c r="R4" s="46"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
       <c r="H5" s="1"/>
       <c r="I5" s="44"/>
       <c r="J5" s="45"/>
@@ -1708,13 +1682,13 @@
       <c r="R5" s="46"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="1"/>
       <c r="I6" s="44"/>
       <c r="J6" s="45"/>
@@ -1728,13 +1702,13 @@
       <c r="R6" s="46"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
       <c r="H7" s="1"/>
       <c r="I7" s="44"/>
       <c r="J7" s="45"/>
@@ -1748,13 +1722,13 @@
       <c r="R7" s="46"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
       <c r="H8" s="1"/>
       <c r="I8" s="44"/>
       <c r="J8" s="45"/>
@@ -1768,13 +1742,13 @@
       <c r="R8" s="46"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
       <c r="H9" s="1"/>
       <c r="I9" s="44"/>
       <c r="J9" s="45"/>
@@ -1788,21 +1762,21 @@
       <c r="R9" s="46"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25" t="s">
+      <c r="A10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="B10" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="28"/>
       <c r="H10" s="1"/>
       <c r="I10" s="44"/>
       <c r="J10" s="45"/>
@@ -1816,24 +1790,24 @@
       <c r="R10" s="46"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A11" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31" t="s">
+      <c r="A11" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="B11" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="C11" s="31"/>
+      <c r="D11" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>23</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="44"/>
@@ -1848,24 +1822,24 @@
       <c r="R11" s="46"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A12" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="31" t="s">
+      <c r="A12" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="C12" s="33"/>
+      <c r="D12" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>29</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="44"/>
@@ -1880,17 +1854,17 @@
       <c r="R12" s="46"/>
     </row>
     <row r="13" ht="70" customHeight="1" spans="1:18">
-      <c r="A13" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33" t="s">
-        <v>31</v>
-      </c>
+      <c r="A13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="9"/>
       <c r="I13" s="47"/>
       <c r="J13" s="45"/>
       <c r="K13" s="46"/>
@@ -1923,7 +1897,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="90" customHeight="1" spans="1:18">
       <c r="A15" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -1941,23 +1915,27 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="50" customHeight="1" spans="1:18">
+    <row r="16" s="1" customFormat="1" ht="67" customHeight="1" spans="1:18">
       <c r="A16" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="E16" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="44"/>
@@ -1971,25 +1949,25 @@
       <c r="Q16" s="46"/>
       <c r="R16" s="5"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="57" customHeight="1" spans="1:18">
-      <c r="A17" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>6</v>
+    <row r="17" s="1" customFormat="1" ht="64" customHeight="1" spans="1:18">
+      <c r="A17" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="17" t="s">
         <v>9</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>11</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="44"/>
@@ -2004,24 +1982,24 @@
       <c r="R17" s="5"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A18" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="18" t="s">
+      <c r="B18" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="C18" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="D18" s="21"/>
+      <c r="E18" s="19" t="s">
         <v>41</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="44"/>
@@ -2036,13 +2014,13 @@
       <c r="R18" s="5"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
       <c r="C19" s="37"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="4"/>
@@ -2056,13 +2034,13 @@
       <c r="R19" s="5"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
       <c r="C20" s="38"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="4"/>
@@ -2076,13 +2054,13 @@
       <c r="R20" s="5"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="38"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="4"/>
@@ -2096,13 +2074,13 @@
       <c r="R21" s="5"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="38"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="4"/>
@@ -2116,13 +2094,13 @@
       <c r="R22" s="5"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A23" s="28"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="36"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="1"/>
       <c r="I23" s="44"/>
       <c r="J23" s="45"/>
@@ -2136,24 +2114,24 @@
       <c r="R23" s="5"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="77" customHeight="1" spans="1:18">
-      <c r="A24" s="28" t="s">
-        <v>14</v>
+      <c r="A24" s="29" t="s">
+        <v>16</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C24" s="40"/>
-      <c r="D24" s="31" t="s">
-        <v>43</v>
+      <c r="D24" s="32" t="s">
+        <v>45</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -2168,17 +2146,17 @@
       <c r="R24" s="5"/>
     </row>
     <row r="25" ht="73" customHeight="1" spans="1:7">
-      <c r="A25" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33" t="s">
-        <v>31</v>
-      </c>
+      <c r="A25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="9"/>
     </row>
     <row r="26" ht="50.1" customHeight="1"/>
     <row r="27" ht="54.95" customHeight="1" spans="9:18">
@@ -2322,7 +2300,6 @@
   </sheetData>
   <mergeCells count="51">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:R2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="K3:R3"/>
@@ -2345,11 +2322,11 @@
     <mergeCell ref="K11:R11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="K12:R12"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="K14:R14"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:B16"/>
     <mergeCell ref="K16:Q16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="K17:Q17"/>
@@ -2362,7 +2339,8 @@
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="K23:Q23"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="K27:R27"/>
     <mergeCell ref="K28:R28"/>
     <mergeCell ref="K29:R29"/>
@@ -2377,7 +2355,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C2 B16:C16 B11:B12 G11:G12"/>
   </dataValidations>
   <pageMargins left="0.314583333333333" right="0.118055555555556" top="0.354166666666667" bottom="0.196527777777778" header="0.298611111111111" footer="0.298611111111111"/>
-  <pageSetup paperSize="9" scale="41" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="38" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -62,15 +62,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <si>
     <t>费用报销单</t>
   </si>
   <si>
-    <t>单位：</t>
-  </si>
-  <si>
-    <t>{unit}</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单位：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{unit}</t>
+    </r>
   </si>
   <si>
     <t>部门：</t>
@@ -94,7 +109,8 @@
     <t>摘要</t>
   </si>
   <si>
-    <t>金额(含税)</t>
+    <t>金额
+(含税)</t>
   </si>
   <si>
     <t>备注</t>
@@ -169,6 +185,12 @@
   </si>
   <si>
     <t>成本一览表</t>
+  </si>
+  <si>
+    <t>单位：</t>
+  </si>
+  <si>
+    <t>{unit}</t>
   </si>
   <si>
     <t>编号合同名称</t>
@@ -1026,104 +1048,104 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1538,13 +1560,13 @@
   <dimension ref="A1:R41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26.8333333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="39.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="55.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="62.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.1" style="2" customWidth="1"/>
+    <col min="4" max="4" width="61" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="36.375" style="4" customWidth="1"/>
     <col min="11" max="18" width="9" style="5"/>
   </cols>
@@ -1575,23 +1597,21 @@
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>7</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="44"/>
@@ -1606,20 +1626,20 @@
       <c r="R2" s="46"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>10</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>11</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="44"/>
@@ -1634,20 +1654,20 @@
       <c r="R3" s="46"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>14</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>15</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="44"/>
@@ -1662,13 +1682,13 @@
       <c r="R4" s="46"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="1"/>
       <c r="I5" s="44"/>
       <c r="J5" s="45"/>
@@ -1682,13 +1702,13 @@
       <c r="R5" s="46"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A6" s="19"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
       <c r="H6" s="1"/>
       <c r="I6" s="44"/>
       <c r="J6" s="45"/>
@@ -1702,13 +1722,13 @@
       <c r="R6" s="46"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
       <c r="H7" s="1"/>
       <c r="I7" s="44"/>
       <c r="J7" s="45"/>
@@ -1722,13 +1742,13 @@
       <c r="R7" s="46"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A8" s="19"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
       <c r="H8" s="1"/>
       <c r="I8" s="44"/>
       <c r="J8" s="45"/>
@@ -1742,13 +1762,13 @@
       <c r="R8" s="46"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
       <c r="H9" s="1"/>
       <c r="I9" s="44"/>
       <c r="J9" s="45"/>
@@ -1762,21 +1782,21 @@
       <c r="R9" s="46"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26" t="s">
+      <c r="F10" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="28"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="1"/>
       <c r="I10" s="44"/>
       <c r="J10" s="45"/>
@@ -1790,24 +1810,24 @@
       <c r="R10" s="46"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="C11" s="30"/>
+      <c r="D11" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32" t="s">
+      <c r="E11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="F11" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="G11" s="18" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>25</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="44"/>
@@ -1822,24 +1842,24 @@
       <c r="R11" s="46"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="80" customHeight="1" spans="1:18">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="32" t="s">
+      <c r="E12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="F12" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="G12" s="18" t="s">
         <v>30</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="44"/>
@@ -1854,17 +1874,17 @@
       <c r="R12" s="46"/>
     </row>
     <row r="13" ht="70" customHeight="1" spans="1:18">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="9"/>
+      <c r="G13" s="33"/>
       <c r="I13" s="47"/>
       <c r="J13" s="45"/>
       <c r="K13" s="46"/>
@@ -1897,7 +1917,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="90" customHeight="1" spans="1:18">
       <c r="A15" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -1917,25 +1937,25 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="67" customHeight="1" spans="1:18">
       <c r="A16" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="D16" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="F16" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="G16" s="13" t="s">
         <v>6</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>7</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="44"/>
@@ -1950,24 +1970,24 @@
       <c r="R16" s="5"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="64" customHeight="1" spans="1:18">
-      <c r="A17" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="15" t="s">
+      <c r="A17" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="18" t="s">
+      <c r="D17" s="15"/>
+      <c r="E17" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>11</v>
+      <c r="F17" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="44"/>
@@ -1981,25 +2001,25 @@
       <c r="Q17" s="46"/>
       <c r="R17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A18" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="19" t="s">
+    <row r="18" s="1" customFormat="1" ht="133" customHeight="1" spans="1:18">
+      <c r="A18" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="B18" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="19" t="s">
+      <c r="C18" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="D18" s="20"/>
+      <c r="E18" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="F18" s="18" t="s">
         <v>43</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="44"/>
@@ -2014,13 +2034,13 @@
       <c r="R18" s="5"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="37"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="4"/>
@@ -2034,13 +2054,13 @@
       <c r="R19" s="5"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="38"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="4"/>
@@ -2054,13 +2074,13 @@
       <c r="R20" s="5"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="38"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="4"/>
@@ -2074,13 +2094,13 @@
       <c r="R21" s="5"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="38"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="4"/>
@@ -2094,13 +2114,13 @@
       <c r="R22" s="5"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="132" customHeight="1" spans="1:18">
-      <c r="A23" s="29"/>
-      <c r="B23" s="15"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="36"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="1"/>
       <c r="I23" s="44"/>
       <c r="J23" s="45"/>
@@ -2114,24 +2134,24 @@
       <c r="R23" s="5"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="77" customHeight="1" spans="1:18">
-      <c r="A24" s="29" t="s">
-        <v>16</v>
+      <c r="A24" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="40"/>
-      <c r="D24" s="32" t="s">
-        <v>45</v>
+      <c r="D24" s="31" t="s">
+        <v>46</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -2146,17 +2166,17 @@
       <c r="R24" s="5"/>
     </row>
     <row r="25" ht="73" customHeight="1" spans="1:7">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="9"/>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" ht="50.1" customHeight="1"/>
     <row r="27" ht="54.95" customHeight="1" spans="9:18">
@@ -2298,8 +2318,9 @@
     </row>
     <row r="41" ht="29.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="52">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:R2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="K3:R3"/>
@@ -2355,7 +2376,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C2 B16:C16 B11:B12 G11:G12"/>
   </dataValidations>
   <pageMargins left="0.314583333333333" right="0.118055555555556" top="0.354166666666667" bottom="0.196527777777778" header="0.298611111111111" footer="0.298611111111111"/>
-  <pageSetup paperSize="9" scale="38" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="39" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/FeeTemplate.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>费用报销单</t>
   </si>
@@ -187,12 +187,6 @@
     <t>成本一览表</t>
   </si>
   <si>
-    <t>单位：</t>
-  </si>
-  <si>
-    <t>{unit}</t>
-  </si>
-  <si>
     <t>编号合同名称</t>
   </si>
   <si>
@@ -451,12 +445,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1896,7 +1890,7 @@
       <c r="Q13" s="46"/>
       <c r="R13" s="46"/>
     </row>
-    <row r="14" ht="90" customHeight="1" spans="1:18">
+    <row r="14" ht="142" customHeight="1" spans="1:18">
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="35"/>
@@ -1937,11 +1931,9 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="67" customHeight="1" spans="1:18">
       <c r="A16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>35</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
         <v>2</v>
       </c>
@@ -1971,7 +1963,7 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="64" customHeight="1" spans="1:18">
       <c r="A17" s="28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>7</v>
@@ -1981,10 +1973,10 @@
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>10</v>
@@ -2003,23 +1995,23 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="133" customHeight="1" spans="1:18">
       <c r="A18" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>44</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="44"/>
@@ -2138,20 +2130,20 @@
         <v>15</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F24" s="42" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -2318,7 +2310,7 @@
     </row>
     <row r="41" ht="29.1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="53">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:R2"/>
@@ -2348,6 +2340,7 @@
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="K14:R14"/>
     <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="K16:Q16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="K17:Q17"/>
@@ -2375,7 +2368,7 @@
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C2 B16:C16 B11:B12 G11:G12"/>
   </dataValidations>
-  <pageMargins left="0.314583333333333" right="0.118055555555556" top="0.354166666666667" bottom="0.196527777777778" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageMargins left="0.314583333333333" right="0.118055555555556" top="0.393055555555556" bottom="0.196527777777778" header="0.298611111111111" footer="0.298611111111111"/>
   <pageSetup paperSize="9" scale="39" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId2"/>
